--- a/Donnees/Statistiques Démographiques et sociales/Santé/Infrastructures de Santé-Francais.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Santé/Infrastructures de Santé-Francais.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\2025\Annuaire des Statistiques Socio-démographiques_Edition 2025_VP\Atelier de Finalisation et Validation de l'Annuaire 2025\Portail DSDSG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Santé\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C35EDF-8128-44CD-A5A7-AB486AFC7807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA605909-1263-4C4E-AA61-3AE06E986289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Centres de Santé" sheetId="2" r:id="rId1"/>
@@ -21,15 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -100,16 +91,16 @@
     <t>Tableau : Evolution du nombre de centres de santé par Wilaya durant la période 2014-2024</t>
   </si>
   <si>
-    <t>Tableau : Evolution du nombre de postes de santé par Wilaya durant la période 2014-2024</t>
-  </si>
-  <si>
     <t>Hodh Chargui</t>
   </si>
   <si>
-    <t>Source : Annuaires des Statistiques Sanitaires/MS</t>
-  </si>
-  <si>
     <t>Wilaya</t>
+  </si>
+  <si>
+    <t>Source : MS/Annuaires des Statistiques Sanitaires</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.1 : Evolution du nombre de centres de santé par Wilaya durant la période 2014-2024</t>
   </si>
 </sst>
 </file>
@@ -542,20 +533,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24361140-DBD2-45F7-802A-5345D767F2C0}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="27" x14ac:dyDescent="0.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="26.4" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="30.08984375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="30.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="12" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="11" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9.08984375" style="2"/>
+    <col min="12" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -570,7 +561,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A2" s="5"/>
       <c r="B2" s="6">
         <v>2014</v>
@@ -603,7 +594,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -638,7 +629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
@@ -673,7 +664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
@@ -708,7 +699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -743,7 +734,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
@@ -778,7 +769,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -813,7 +804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
@@ -848,7 +839,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -883,7 +874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A11" s="5" t="s">
         <v>7</v>
       </c>
@@ -918,7 +909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -953,7 +944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A13" s="5" t="s">
         <v>19</v>
       </c>
@@ -988,7 +979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
@@ -1023,7 +1014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1058,7 +1049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A16" s="5" t="s">
         <v>10</v>
       </c>
@@ -1093,7 +1084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
@@ -1128,7 +1119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A18" s="11" t="s">
         <v>13</v>
       </c>
@@ -1166,7 +1157,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A19" s="16" t="s">
         <v>23</v>
       </c>
@@ -1181,21 +1172,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{724C3478-CE4E-4B94-9D0B-152B7CDC098E}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="27" x14ac:dyDescent="0.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="26.4" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="30.08984375" style="2" customWidth="1"/>
-    <col min="2" max="3" width="14.453125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="30.109375" style="2" customWidth="1"/>
+    <col min="2" max="3" width="14.44140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="12" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="11" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9.08984375" style="2"/>
+    <col min="12" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1208,9 +1199,9 @@
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A2" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="6">
         <v>2014</v>
@@ -1243,9 +1234,9 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A3" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="8">
         <v>124</v>
@@ -1278,7 +1269,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
@@ -1313,7 +1304,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
@@ -1348,7 +1339,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -1383,7 +1374,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
@@ -1418,7 +1409,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -1453,7 +1444,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
@@ -1488,7 +1479,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
@@ -1523,7 +1514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A11" s="5" t="s">
         <v>7</v>
       </c>
@@ -1558,7 +1549,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -1593,7 +1584,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -1628,7 +1619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
@@ -1663,7 +1654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1698,7 +1689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A16" s="5" t="s">
         <v>10</v>
       </c>
@@ -1733,7 +1724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
@@ -1768,7 +1759,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A18" s="11" t="s">
         <v>17</v>
       </c>
@@ -1808,7 +1799,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.9">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A19" s="16" t="s">
         <v>23</v>
       </c>
